--- a/docs/助成金2026/講師要件確認書_桑畑健_記入済.xlsx
+++ b/docs/助成金2026/講師要件確認書_桑畑健_記入済.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="78">
   <si>
     <t>年</t>
     <rPh sb="0" eb="1">
@@ -1002,27 +1002,40 @@
     <t xml:space="preserve">○</t>
   </si>
   <si>
-    <t xml:space="preserve">2008年5月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現在</t>
-  </si>
-  <si>
-    <t xml:space="preserve">株式会社医療Design Workshop（旧社名：Jump Start株式会社）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">代表取締役／クリエイティブ・ディレクター
-企業の業務課題の整理と、その解決の仕組みづくりの企画・設計に従事。業務プロセスの分析、改善方針の立案、システム化の設計・導入までを一貫して担当。</t>
+    <t xml:space="preserve">2008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">株式会社医療Design Workshop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">代表取締役　業務改善の企画・設計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
   </si>
   <si>
     <t xml:space="preserve">一般社団法人日本医療デザインセンター</t>
   </si>
   <si>
-    <t xml:space="preserve">代表理事
-医療・介護分野の業務改善プロジェクトの企画・設計を統括。全国30以上のプロジェクトを同時展開。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018年4月</t>
+    <t xml:space="preserve">代表理事　業務改善事業の統括</t>
   </si>
 </sst>
 </file>
@@ -5579,7 +5592,9 @@
       <c r="D34" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="E34" s="7"/>
+      <c r="E34" s="7" t="s">
+        <v>67</v>
+      </c>
       <c r="F34" s="71" t="s">
         <v>5</v>
       </c>
@@ -5587,29 +5602,35 @@
         <v>6</v>
       </c>
       <c r="H34" s="93" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I34" s="93"/>
       <c r="J34" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="K34" s="7"/>
+      <c r="K34" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="L34" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="M34" s="93"/>
+      <c r="M34" s="93" t="s">
+        <v>70</v>
+      </c>
       <c r="N34" s="93"/>
       <c r="O34" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="P34" s="110"/>
+      <c r="P34" s="110" t="s">
+        <v>71</v>
+      </c>
       <c r="Q34" s="110"/>
       <c r="R34" s="111" t="s">
         <v>22</v>
       </c>
       <c r="S34" s="112"/>
       <c r="T34" s="94" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="U34" s="94"/>
       <c r="V34" s="94"/>
@@ -5621,7 +5642,7 @@
       <c r="AB34" s="94"/>
       <c r="AC34" s="94"/>
       <c r="AD34" s="90" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AE34" s="90"/>
       <c r="AF34" s="90"/>
@@ -5638,13 +5659,15 @@
         <v>54</v>
       </c>
       <c r="B35" s="92" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C35" s="93"/>
       <c r="D35" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="E35" s="7"/>
+      <c r="E35" s="7" t="s">
+        <v>71</v>
+      </c>
       <c r="F35" s="71" t="s">
         <v>5</v>
       </c>
@@ -5652,29 +5675,35 @@
         <v>6</v>
       </c>
       <c r="H35" s="93" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I35" s="93"/>
       <c r="J35" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="K35" s="7"/>
+      <c r="K35" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="L35" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="M35" s="93"/>
+      <c r="M35" s="93" t="s">
+        <v>75</v>
+      </c>
       <c r="N35" s="93"/>
       <c r="O35" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="P35" s="110"/>
+      <c r="P35" s="110" t="s">
+        <v>67</v>
+      </c>
       <c r="Q35" s="110"/>
       <c r="R35" s="111" t="s">
         <v>22</v>
       </c>
       <c r="S35" s="112"/>
       <c r="T35" s="90" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="U35" s="90"/>
       <c r="V35" s="90"/>
@@ -5686,7 +5715,7 @@
       <c r="AB35" s="90"/>
       <c r="AC35" s="90"/>
       <c r="AD35" s="90" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="AE35" s="90"/>
       <c r="AF35" s="90"/>
